--- a/data/trans_orig/P74B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P74B-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su pareja percibe algún tipo de pensión en 2007</t>
+          <t>Población según si su pareja percibe algún tipo de pensión en 2007 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64307</t>
+          <t>64772</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95751</t>
+          <t>97029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>388057</t>
+          <t>388029</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>416172</t>
+          <t>416052</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>451808</t>
+          <t>452289</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>513570</t>
+          <t>517652</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,71%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>512217</t>
+          <t>510939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>543661</t>
+          <t>543196</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38598</t>
+          <t>38718</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66713</t>
+          <t>66741</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>549168</t>
+          <t>545086</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>610930</t>
+          <t>610449</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,44%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11229</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29061</t>
+          <t>29057</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76106</t>
+          <t>76270</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98500</t>
+          <t>98773</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86971</t>
+          <t>88076</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127484</t>
+          <t>127631</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>624296</t>
+          <t>624300</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>642128</t>
+          <t>642486</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40083</t>
+          <t>39810</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62477</t>
+          <t>62313</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>664456</t>
+          <t>664309</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>704969</t>
+          <t>703864</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,88%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18386</t>
+          <t>19350</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>11461</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17804</t>
+          <t>17798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16368</t>
+          <t>17598</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37049</t>
+          <t>37611</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135801</t>
+          <t>134837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149861</t>
+          <t>149361</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135861</t>
+          <t>135299</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>156542</t>
+          <t>155312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87757</t>
+          <t>87341</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128470</t>
+          <t>128270</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>488369</t>
+          <t>487602</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>524803</t>
+          <t>524709</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>574679</t>
+          <t>573623</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>654034</t>
+          <t>658317</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1287042</t>
+          <t>1287242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1327755</t>
+          <t>1328171</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>87273</t>
+          <t>87367</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>123707</t>
+          <t>124474</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1373554</t>
+          <t>1369271</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1452909</t>
+          <t>1453965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su pareja percibe algún tipo de pensión en 2012</t>
+          <t>Población según si su pareja percibe algún tipo de pensión en 2012 (tasa de respuesta: 97,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89943</t>
+          <t>90658</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129661</t>
+          <t>129159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>425195</t>
+          <t>427730</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>465156</t>
+          <t>465103</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>522491</t>
+          <t>524264</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>590690</t>
+          <t>591607</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,49%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>419318</t>
+          <t>419820</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>459036</t>
+          <t>458321</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91927</t>
+          <t>91980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131888</t>
+          <t>129353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>515373</t>
+          <t>514456</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>583572</t>
+          <t>581799</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,6%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35273</t>
+          <t>36577</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66869</t>
+          <t>67093</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>133844</t>
+          <t>134004</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>172781</t>
+          <t>171680</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>178243</t>
+          <t>176675</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>232810</t>
+          <t>232028</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>645015</t>
+          <t>644791</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>676611</t>
+          <t>675307</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>144847</t>
+          <t>145948</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>183784</t>
+          <t>183624</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>796701</t>
+          <t>797483</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>851268</t>
+          <t>852836</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22917</t>
+          <t>23201</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>18122</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31866</t>
+          <t>32167</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27361</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52281</t>
+          <t>52858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,57%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90539</t>
+          <t>90255</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107562</t>
+          <t>106457</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>11813</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25831</t>
+          <t>25858</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105155</t>
+          <t>104578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>130075</t>
+          <t>129355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>147776</t>
+          <t>149096</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>200069</t>
+          <t>200779</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>594825</t>
+          <t>595942</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>651059</t>
+          <t>654384</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>751649</t>
+          <t>751694</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>842557</t>
+          <t>845500</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1174250</t>
+          <t>1173540</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1226543</t>
+          <t>1225223</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>267632</t>
+          <t>264307</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>323866</t>
+          <t>322749</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1450453</t>
+          <t>1447510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1541361</t>
+          <t>1541316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su pareja percibe algún tipo de pensión en 2016</t>
+          <t>Población según si su pareja percibe algún tipo de pensión en 2016 (tasa de respuesta: 94,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64095</t>
+          <t>65865</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94440</t>
+          <t>94521</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>334501</t>
+          <t>334599</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>369200</t>
+          <t>369797</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>403624</t>
+          <t>402707</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>460027</t>
+          <t>460335</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,11%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>312427</t>
+          <t>312346</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>342772</t>
+          <t>341002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74689</t>
+          <t>74092</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109388</t>
+          <t>109290</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>390729</t>
+          <t>390421</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>447132</t>
+          <t>448049</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,66%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55128</t>
+          <t>55160</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88229</t>
+          <t>89204</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>190459</t>
+          <t>190601</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>232344</t>
+          <t>230846</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>254720</t>
+          <t>252248</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>316584</t>
+          <t>311277</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>709320</t>
+          <t>708345</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>742421</t>
+          <t>742389</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>162379</t>
+          <t>163877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>204264</t>
+          <t>204122</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>875687</t>
+          <t>880994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>937551</t>
+          <t>940023</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,84%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12439</t>
+          <t>12504</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29762</t>
+          <t>30024</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18516</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35243</t>
+          <t>35116</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35104</t>
+          <t>36592</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61905</t>
+          <t>61291</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118047</t>
+          <t>117785</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135370</t>
+          <t>135305</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21513</t>
+          <t>21640</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38240</t>
+          <t>37643</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142659</t>
+          <t>143273</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>169460</t>
+          <t>167972</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,11%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>144049</t>
+          <t>146648</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>193826</t>
+          <t>197687</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>561562</t>
+          <t>561351</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>620439</t>
+          <t>622317</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>715522</t>
+          <t>715552</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>804886</t>
+          <t>810092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1158398</t>
+          <t>1154537</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1208175</t>
+          <t>1205576</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>274928</t>
+          <t>273050</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>333805</t>
+          <t>334016</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1442705</t>
+          <t>1437499</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1532069</t>
+          <t>1532039</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/P74B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P74B-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64772</t>
+          <t>64323</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97029</t>
+          <t>97246</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>388029</t>
+          <t>389248</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>416052</t>
+          <t>415734</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>452289</t>
+          <t>450384</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>517652</t>
+          <t>513983</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>510939</t>
+          <t>510722</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>543196</t>
+          <t>543645</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38718</t>
+          <t>39036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66741</t>
+          <t>65522</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>545086</t>
+          <t>548755</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>610449</t>
+          <t>612354</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10871</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29057</t>
+          <t>29872</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76270</t>
+          <t>76268</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98773</t>
+          <t>98415</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88076</t>
+          <t>86817</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127631</t>
+          <t>126669</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>624300</t>
+          <t>623485</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>642486</t>
+          <t>642996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39810</t>
+          <t>40168</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62313</t>
+          <t>62315</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>664309</t>
+          <t>665271</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>703864</t>
+          <t>705123</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19350</t>
+          <t>18501</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11461</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17798</t>
+          <t>17806</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37611</t>
+          <t>37360</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134837</t>
+          <t>135686</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149361</t>
+          <t>150057</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>917</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135299</t>
+          <t>135550</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155312</t>
+          <t>156002</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87341</t>
+          <t>88479</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128270</t>
+          <t>128871</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>487602</t>
+          <t>486902</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>524709</t>
+          <t>525540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>573623</t>
+          <t>573265</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>658317</t>
+          <t>654471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1287242</t>
+          <t>1286641</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1328171</t>
+          <t>1327033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>87367</t>
+          <t>86536</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124474</t>
+          <t>125174</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1369271</t>
+          <t>1373117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1453965</t>
+          <t>1454323</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90658</t>
+          <t>91101</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129159</t>
+          <t>132383</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>427730</t>
+          <t>426390</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>465103</t>
+          <t>464323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>524264</t>
+          <t>524233</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>591607</t>
+          <t>593510</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,66%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>419820</t>
+          <t>416596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>458321</t>
+          <t>457878</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91980</t>
+          <t>92760</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129353</t>
+          <t>130693</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>514456</t>
+          <t>512553</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>581799</t>
+          <t>581830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36577</t>
+          <t>37681</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67093</t>
+          <t>70450</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134004</t>
+          <t>131674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>171680</t>
+          <t>171211</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>176675</t>
+          <t>178829</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>232028</t>
+          <t>230295</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>644791</t>
+          <t>641434</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>675307</t>
+          <t>674203</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>145948</t>
+          <t>146417</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>183624</t>
+          <t>185954</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>797483</t>
+          <t>799216</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>852836</t>
+          <t>850682</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23201</t>
+          <t>24737</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18122</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32167</t>
+          <t>33131</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28081</t>
+          <t>28324</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52858</t>
+          <t>52670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90255</t>
+          <t>88719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106457</t>
+          <t>106966</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11813</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25858</t>
+          <t>25414</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104578</t>
+          <t>104766</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>129355</t>
+          <t>129112</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>149096</t>
+          <t>147053</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>200779</t>
+          <t>202571</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>595942</t>
+          <t>596811</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>654384</t>
+          <t>652904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>751694</t>
+          <t>749077</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>845500</t>
+          <t>841711</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1173540</t>
+          <t>1171748</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1225223</t>
+          <t>1227266</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>264307</t>
+          <t>265787</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>322749</t>
+          <t>321880</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1447510</t>
+          <t>1451299</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1541316</t>
+          <t>1543933</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,33%</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65865</t>
+          <t>63440</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94521</t>
+          <t>95166</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>334599</t>
+          <t>335598</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>369797</t>
+          <t>369680</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>402707</t>
+          <t>400745</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>460335</t>
+          <t>458381</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,88%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>312346</t>
+          <t>311701</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>341002</t>
+          <t>343427</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74092</t>
+          <t>74209</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109290</t>
+          <t>108291</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>390421</t>
+          <t>392375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>448049</t>
+          <t>450011</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,9%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55160</t>
+          <t>54033</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89204</t>
+          <t>87482</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>190601</t>
+          <t>190688</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>230846</t>
+          <t>231314</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>252248</t>
+          <t>253119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>311277</t>
+          <t>312098</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>708345</t>
+          <t>710067</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>742389</t>
+          <t>743516</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>163877</t>
+          <t>163409</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>204122</t>
+          <t>204035</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>880994</t>
+          <t>880173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>940023</t>
+          <t>939152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,77%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12504</t>
+          <t>12311</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30024</t>
+          <t>30212</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19113</t>
+          <t>18902</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35116</t>
+          <t>34823</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36592</t>
+          <t>36312</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61291</t>
+          <t>62106</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117785</t>
+          <t>117597</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135305</t>
+          <t>135498</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21640</t>
+          <t>21933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37643</t>
+          <t>37854</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>143273</t>
+          <t>142458</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>167972</t>
+          <t>168252</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,25%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>146648</t>
+          <t>144249</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>197687</t>
+          <t>193839</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>561351</t>
+          <t>563172</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>622317</t>
+          <t>622501</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>715552</t>
+          <t>715717</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>810092</t>
+          <t>811511</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,11%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1154537</t>
+          <t>1158385</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1205576</t>
+          <t>1207975</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>273050</t>
+          <t>272866</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>334016</t>
+          <t>332195</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1437499</t>
+          <t>1436080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1532039</t>
+          <t>1531874</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
